--- a/data/obx_xlsx/PENR.OL.xlsx
+++ b/data/obx_xlsx/PENR.OL.xlsx
@@ -9633,10 +9633,10 @@
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
       <c r="D82" s="15">
-        <v>200.8</v>
+        <v>199.68</v>
       </c>
       <c r="E82" s="15">
-        <v>129.58</v>
+        <v>127.55</v>
       </c>
       <c r="F82" s="16">
         <v>37.07</v>
@@ -9663,12 +9663,8 @@
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
-      <c r="D83" s="15">
-        <v>199.68</v>
-      </c>
-      <c r="E83" s="15">
-        <v>127.55</v>
-      </c>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
       <c r="F83" s="17"/>
       <c r="G83" s="17"/>
       <c r="H83" s="17"/>
